--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_02.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results_run_02.xlsx
@@ -38027,7 +38027,7 @@
         <v>2</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="408">
@@ -38779,7 +38779,7 @@
         <v>3</v>
       </c>
       <c r="AD415" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="416">
@@ -39146,7 +39146,7 @@
         <v>0.96</v>
       </c>
       <c r="AA419" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="AB419" t="n">
         <v>0.35</v>
@@ -39155,7 +39155,7 @@
         <v>2</v>
       </c>
       <c r="AD419" t="n">
-        <v>0.8175</v>
+        <v>0.8335</v>
       </c>
     </row>
     <row r="420">
@@ -39240,7 +39240,7 @@
         <v>0.88</v>
       </c>
       <c r="AA420" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB420" t="n">
         <v>0.64</v>
@@ -39249,7 +39249,7 @@
         <v>1</v>
       </c>
       <c r="AD420" t="n">
-        <v>0.855</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="421">
@@ -39334,7 +39334,7 @@
         <v>0.77</v>
       </c>
       <c r="AA421" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AB421" t="n">
         <v>0.85</v>
@@ -39343,7 +39343,7 @@
         <v>3</v>
       </c>
       <c r="AD421" t="n">
-        <v>0.8109999999999999</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="422">
@@ -39437,7 +39437,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="423">
@@ -39522,7 +39522,7 @@
         <v>0.58</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -39531,7 +39531,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="424">
@@ -39616,7 +39616,7 @@
         <v>0.38</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -39625,7 +39625,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="425">
@@ -39813,7 +39813,7 @@
         <v>1</v>
       </c>
       <c r="AD426" t="n">
-        <v>0.8119999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="427">
@@ -39907,7 +39907,7 @@
         <v>2</v>
       </c>
       <c r="AD427" t="n">
-        <v>0.7999999999999998</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="428">
@@ -40095,7 +40095,7 @@
         <v>2</v>
       </c>
       <c r="AD429" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="430">
@@ -40180,7 +40180,7 @@
         <v>0.58</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -40189,7 +40189,7 @@
         <v>3</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="431">
@@ -40377,7 +40377,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -40556,7 +40556,7 @@
         <v>0.13</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -40565,7 +40565,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.2865</v>
+        <v>0.2885</v>
       </c>
     </row>
     <row r="435">
@@ -40650,7 +40650,7 @@
         <v>0</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -40659,7 +40659,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.2605000000000001</v>
+        <v>0.2785</v>
       </c>
     </row>
     <row r="436">
@@ -40744,7 +40744,7 @@
         <v>0</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -40753,7 +40753,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.162</v>
+        <v>0.188</v>
       </c>
     </row>
     <row r="437">
@@ -41129,7 +41129,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6469999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="441">
@@ -41214,7 +41214,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -41223,7 +41223,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -41308,7 +41308,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -41317,7 +41317,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -41505,7 +41505,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
     </row>
     <row r="445">
@@ -41778,7 +41778,7 @@
         <v>0</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -41787,7 +41787,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.2675</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="448">
@@ -41872,7 +41872,7 @@
         <v>0</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -41881,7 +41881,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="449">
@@ -42248,7 +42248,7 @@
         <v>0.23</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -42257,7 +42257,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.3560000000000001</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="453">
@@ -42342,7 +42342,7 @@
         <v>0</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -42351,7 +42351,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
     </row>
     <row r="454">
@@ -42436,7 +42436,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -42445,7 +42445,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -42633,7 +42633,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="457">
@@ -42727,7 +42727,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="458">
@@ -43291,7 +43291,7 @@
         <v>3</v>
       </c>
       <c r="AD463" t="n">
-        <v>0.6749999999999999</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="464">
@@ -43573,7 +43573,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="467">
@@ -43658,7 +43658,7 @@
         <v>0.64</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -43667,7 +43667,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="468">
@@ -43752,7 +43752,7 @@
         <v>0.38</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -43761,7 +43761,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="469">
@@ -43846,7 +43846,7 @@
         <v>0.19</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -43855,7 +43855,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="470">
@@ -44043,7 +44043,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="472">
@@ -44137,7 +44137,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="473">
@@ -44325,7 +44325,7 @@
         <v>2</v>
       </c>
       <c r="AD474" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="475">
@@ -44513,7 +44513,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.7615000000000001</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="477">
@@ -44889,7 +44889,7 @@
         <v>2</v>
       </c>
       <c r="AD480" t="n">
-        <v>0.6729999999999999</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="481">
@@ -44974,7 +44974,7 @@
         <v>0.51</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -44983,7 +44983,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="482">
@@ -45077,7 +45077,7 @@
         <v>1</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7589999999999999</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="483">
@@ -45256,7 +45256,7 @@
         <v>0.19</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -45265,7 +45265,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.3235</v>
+        <v>0.3375</v>
       </c>
     </row>
     <row r="485">
@@ -45359,7 +45359,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7555000000000001</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="486">
@@ -45641,7 +45641,7 @@
         <v>1</v>
       </c>
       <c r="AD488" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="489">
@@ -45726,7 +45726,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -45735,7 +45735,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.7010000000000001</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="490">
@@ -45820,7 +45820,7 @@
         <v>0.38</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -45829,7 +45829,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.289</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="491">
@@ -45923,7 +45923,7 @@
         <v>1</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -46111,7 +46111,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.3995000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="494">
@@ -46675,7 +46675,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="500">
@@ -47051,7 +47051,7 @@
         <v>2</v>
       </c>
       <c r="AD503" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="504">
@@ -47700,7 +47700,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -47709,7 +47709,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -47794,7 +47794,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -47803,7 +47803,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -47888,7 +47888,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -47897,7 +47897,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -47982,7 +47982,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -47991,7 +47991,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -48076,7 +48076,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -48085,7 +48085,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -48264,7 +48264,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -48273,7 +48273,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -48358,7 +48358,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -48367,7 +48367,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -48452,7 +48452,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -48461,7 +48461,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -48546,7 +48546,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -48555,7 +48555,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -48640,7 +48640,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -48649,7 +48649,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -48734,7 +48734,7 @@
         <v>0.64</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.46</v>
@@ -48743,7 +48743,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="522">
@@ -48828,7 +48828,7 @@
         <v>0.51</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -48837,7 +48837,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="523">
@@ -48922,7 +48922,7 @@
         <v>0.38</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -48931,7 +48931,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="524">
@@ -49110,7 +49110,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -49119,7 +49119,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -49204,7 +49204,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -49213,7 +49213,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -49401,7 +49401,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -49777,7 +49777,7 @@
         <v>3</v>
       </c>
       <c r="AD532" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="533">
@@ -49965,7 +49965,7 @@
         <v>2</v>
       </c>
       <c r="AD534" t="n">
-        <v>0.6260000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="535">
@@ -50247,7 +50247,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="538">
@@ -50435,7 +50435,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -50623,7 +50623,7 @@
         <v>3</v>
       </c>
       <c r="AD541" t="n">
-        <v>0.6339999999999999</v>
+        <v>0.634</v>
       </c>
     </row>
     <row r="542">
@@ -50896,7 +50896,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -50905,7 +50905,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -50999,7 +50999,7 @@
         <v>3</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -51093,7 +51093,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.8270000000000001</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="547">
@@ -51281,7 +51281,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7374999999999999</v>
+        <v>0.7375</v>
       </c>
     </row>
     <row r="549">
@@ -51563,7 +51563,7 @@
         <v>2</v>
       </c>
       <c r="AD551" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="552">
@@ -51751,7 +51751,7 @@
         <v>3</v>
       </c>
       <c r="AD553" t="n">
-        <v>0.7310000000000001</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="554">
@@ -52033,7 +52033,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -52127,7 +52127,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.6769999999999999</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="558">
@@ -52212,7 +52212,7 @@
         <v>0.64</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -52221,7 +52221,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="559">
@@ -52306,7 +52306,7 @@
         <v>0.51</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -52315,7 +52315,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="560">
@@ -52494,7 +52494,7 @@
         <v>0.51</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -52503,7 +52503,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="562">
@@ -52588,7 +52588,7 @@
         <v>0.38</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -52597,7 +52597,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="563">
@@ -52973,7 +52973,7 @@
         <v>3</v>
       </c>
       <c r="AD566" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="567">
@@ -53161,7 +53161,7 @@
         <v>1</v>
       </c>
       <c r="AD568" t="n">
-        <v>0.8624999999999999</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="569">
@@ -53443,7 +53443,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7609999999999999</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="572">
@@ -53537,7 +53537,7 @@
         <v>1</v>
       </c>
       <c r="AD572" t="n">
-        <v>0.7649999999999999</v>
+        <v>0.765</v>
       </c>
     </row>
     <row r="573">
@@ -53725,7 +53725,7 @@
         <v>3</v>
       </c>
       <c r="AD574" t="n">
-        <v>0.7069999999999999</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="575">
@@ -53819,7 +53819,7 @@
         <v>3</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="576">
@@ -53913,7 +53913,7 @@
         <v>2</v>
       </c>
       <c r="AD576" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="577">
@@ -54101,7 +54101,7 @@
         <v>3</v>
       </c>
       <c r="AD578" t="n">
-        <v>0.7994999999999999</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="579">
@@ -54195,7 +54195,7 @@
         <v>1</v>
       </c>
       <c r="AD579" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="580">
@@ -54289,7 +54289,7 @@
         <v>2</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.8029999999999999</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="581">
@@ -54383,7 +54383,7 @@
         <v>3</v>
       </c>
       <c r="AD581" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="582">
@@ -54477,7 +54477,7 @@
         <v>1</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -54571,7 +54571,7 @@
         <v>2</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.8139999999999998</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -54665,7 +54665,7 @@
         <v>3</v>
       </c>
       <c r="AD584" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="585">
